--- a/upload_data.xlsx
+++ b/upload_data.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Combined" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Combined" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,11 @@
           <t>move_folder</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>related_video</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -461,7 +466,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>E:\storage\905 - Copy (14).mp4</t>
+          <t>E:\storage\903_2.mp4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -469,89 +474,63 @@
           <t>a</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>11/14/2025</t>
+          <t>01/13/2026</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>E:\ghep xong\905 - Copy (14).mp4</t>
+          <t>E:\ghep xong\903_2.mp4</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>a</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>E:\storage\910 - Copy (24).mp4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>f</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>11/14/2025</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>E:\storage\902 - Copy (13).mp4</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>11/14/2025</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>E:\ghep xong\902 - Copy (13).mp4</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>11/14/2025</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>01/13/2026</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>E:\ghep xong\910 - Copy (24).mp4</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
